--- a/data/trans_orig/P79_n_R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R3-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33942</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>30611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30363</t>
+          <t>36027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29805</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>20140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>35627</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46757</t>
+          <t>60199</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>38132</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>56223</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34574</t>
+          <t>52114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76291</t>
+          <t>100502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>360476</t>
+          <t>353811</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>334364</t>
+          <t>327415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>376854</t>
+          <t>372871</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>259359</t>
+          <t>299573</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>237320</t>
+          <t>279412</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>274441</t>
+          <t>319370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>619834</t>
+          <t>653384</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>590709</t>
+          <t>622141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>644467</t>
+          <t>682598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>88,61%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19665</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22923</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34238</t>
+          <t>41282</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>50378</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64123</t>
+          <t>69795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52152</t>
+          <t>59643</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30596</t>
+          <t>45990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70510</t>
+          <t>75692</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>97199</t>
+          <t>110021</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72709</t>
+          <t>89093</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122564</t>
+          <t>139434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>363917</t>
+          <t>409408</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>342232</t>
+          <t>387219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>379378</t>
+          <t>427371</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>447029</t>
+          <t>426099</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>426461</t>
+          <t>408998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>472517</t>
+          <t>441681</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>810946</t>
+          <t>835507</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>782879</t>
+          <t>806101</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>841850</t>
+          <t>858147</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>21100</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>30888</t>
+          <t>41555</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>42685</t>
+          <t>55391</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>59425</t>
+          <t>67563</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44995</t>
+          <t>53051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74500</t>
+          <t>86764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>53788</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>42648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60991</t>
+          <t>67310</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>106470</t>
+          <t>121351</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86481</t>
+          <t>102677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126247</t>
+          <t>144511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>458761</t>
+          <t>528648</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441870</t>
+          <t>509160</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474300</t>
+          <t>545966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>523856</t>
+          <t>542541</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>507911</t>
+          <t>526042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540943</t>
+          <t>556768</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>982617</t>
+          <t>1071189</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>957241</t>
+          <t>1046253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1005969</t>
+          <t>1092047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>42079</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>24103</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28324</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>52907</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64632</t>
+          <t>67897</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56687</t>
+          <t>69435</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>54427</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85895</t>
+          <t>87098</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58058</t>
+          <t>67056</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45544</t>
+          <t>54752</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70571</t>
+          <t>80826</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>114745</t>
+          <t>136491</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>70401</t>
+          <t>116782</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>146266</t>
+          <t>158299</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>804175</t>
+          <t>601455</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>764073</t>
+          <t>582752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>849093</t>
+          <t>618897</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>629517</t>
+          <t>639498</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>614447</t>
+          <t>623984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>645302</t>
+          <t>652596</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1433692</t>
+          <t>1240954</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1391813</t>
+          <t>1215103</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1499478</t>
+          <t>1264169</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13199</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,27 +3071,27 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>18761</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>23800</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>37243</t>
+          <t>43487</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28486</t>
+          <t>33389</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49630</t>
+          <t>56686</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>51188</t>
+          <t>57446</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38724</t>
+          <t>45716</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63497</t>
+          <t>73152</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>60508</t>
+          <t>69818</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49939</t>
+          <t>58077</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72740</t>
+          <t>83919</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>111695</t>
+          <t>127265</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93937</t>
+          <t>109313</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>129647</t>
+          <t>147145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>483103</t>
+          <t>520713</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>467289</t>
+          <t>502490</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>497733</t>
+          <t>535482</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>467947</t>
+          <t>515954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>454473</t>
+          <t>501780</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>479273</t>
+          <t>529297</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>951050</t>
+          <t>1036667</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>928869</t>
+          <t>1014631</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>970141</t>
+          <t>1058399</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,88%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>992</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>992</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25021</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>26589</t>
+          <t>29927</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>39916</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>29718</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>25164</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>42867</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>32674</t>
+          <t>36984</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>53414</t>
+          <t>45976</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>62392</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>57995</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>84917</t>
+          <t>81978</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>325782</t>
+          <t>359938</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>316230</t>
+          <t>348171</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>334834</t>
+          <t>369157</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>560812</t>
+          <t>385709</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>530715</t>
+          <t>375286</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>586640</t>
+          <t>394734</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>886594</t>
+          <t>745646</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>855756</t>
+          <t>729658</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>926988</t>
+          <t>759793</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>596</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,17 +4209,17 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13823</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,22 +4287,22 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>13047</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>22303</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>30004</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26573</t>
+          <t>30178</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>36669</t>
+          <t>42222</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>29334</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>45965</t>
+          <t>53439</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>55879</t>
+          <t>63580</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>51774</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>67216</t>
+          <t>76972</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>253372</t>
+          <t>277600</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>244528</t>
+          <t>267169</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>260252</t>
+          <t>284989</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>376949</t>
+          <t>408744</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>365381</t>
+          <t>397148</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>385641</t>
+          <t>418824</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>630322</t>
+          <t>686344</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>617038</t>
+          <t>671847</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>641193</t>
+          <t>700511</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>36691</t>
+          <t>36819</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>39492</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>42789</t>
+          <t>44916</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>66446</t>
+          <t>62666</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>123153</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>78830</t>
+          <t>101307</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>129856</t>
+          <t>150312</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>129808</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>85867</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>132514</t>
+          <t>153597</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>213650</t>
+          <t>252961</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>178767</t>
+          <t>220220</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>248984</t>
+          <t>285372</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>284135</t>
+          <t>334505</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>227212</t>
+          <t>296308</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>328963</t>
+          <t>371703</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>316467</t>
+          <t>367642</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>258908</t>
+          <t>334313</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>353173</t>
+          <t>401881</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>600602</t>
+          <t>702147</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>516364</t>
+          <t>646586</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>661283</t>
+          <t>752580</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3049587</t>
+          <t>3051574</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2992170</t>
+          <t>3000343</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3137027</t>
+          <t>3096532</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>3265469</t>
+          <t>3218118</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3217920</t>
+          <t>3176703</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3349284</t>
+          <t>3255797</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>6315056</t>
+          <t>6269692</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6237420</t>
+          <t>6207759</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6439604</t>
+          <t>6331232</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
